--- a/Collaudo/Inventario_di_prova_con_difetti.xlsx
+++ b/Collaudo/Inventario_di_prova_con_difetti.xlsx
@@ -435,6 +435,18 @@
   </sheetPr>
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -449,22 +461,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Modello</t>
+          <t>Stato</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Modello/Descrizione</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Numero di serie</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -508,22 +520,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>riga regolare</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>PF4BAU01</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>riga regolare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -552,20 +564,20 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Disponibile</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>senza modello</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>PF4BAU02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Disponibile</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>senza modello</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -604,20 +616,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Controllare</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>8HK903</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Controllare</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>900</v>
@@ -640,18 +652,18 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>verra' scartata</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>senza identificativo</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>verra' scartata</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>800</v>
@@ -674,18 +686,18 @@
           <t>Iphone</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>verra' ignorato</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Apple iPhone 14</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>verra' ignorato</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>356938035643809</t>

--- a/Collaudo/Inventario_di_prova_con_difetti.xlsx
+++ b/Collaudo/Inventario_di_prova_con_difetti.xlsx
@@ -438,8 +438,8 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -461,12 +461,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Stato</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>riga regolare</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Disponibile</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>riga regolare</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>senza modello</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Disponibile</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>senza modello</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -614,12 +614,12 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Controllare</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Dell Latitude 7320 Detachable</t>
@@ -652,12 +652,12 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>verra' scartata</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>senza identificativo</t>
@@ -686,12 +686,12 @@
           <t>Iphone</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>verra' ignorato</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Apple iPhone 14</t>
